--- a/data/excel/event.xlsx
+++ b/data/excel/event.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H11"/>
+  <dimension ref="A1:H13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -805,36 +805,108 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>改革开放</t>
+          <t>渡江战役</t>
         </is>
       </c>
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="inlineStr">
         <is>
+          <t>1949年4月21日</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>人民解放军强渡长江，突破国民党军长江防线，4 月 23 日解放南京。</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>宣告国民党反动统治的覆灭，加速了全国解放的进程。</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>1949 年 4 月人民解放军发起的渡过长江、进军江南的战役。</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>https://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>脱贫攻坚战全面胜利</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>2021年2月25日</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>全国脱贫攻坚总结表彰大会宣告我国脱贫攻坚战取得全面胜利。</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>现行标准下农村贫困人口全部脱贫，历史性地解决了绝对贫困问题。</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2021 年 2 月宣告的脱贫攻坚战全面胜利，是全面建成小康社会的标志性成果。</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>https://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>改革开放</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="inlineStr">
+        <is>
           <t>1978年12月</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>党的十一届三中全会后开启的对内改革、对外开放的历史进程。</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>是决定当代中国命运的关键一招，开辟了中国特色社会主义道路。</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="F13" t="inlineStr">
         <is>
           <t>始于 1978 年的对内改革、对外开放政策，深刻改变了中国面貌。</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>https://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
-        </is>
-      </c>
-      <c r="H11" t="n">
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>https://cpc.people.com.cn/n1/2021/0628/c64387-32142446.html</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
         <v>1</v>
       </c>
     </row>
